--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.00234266687544</v>
+        <v>10.23788068336726</v>
       </c>
       <c r="D2" t="n">
-        <v>62.78446415724981</v>
+        <v>10.20247542555309</v>
       </c>
       <c r="E2" t="n">
-        <v>6.545438624900579</v>
+        <v>1.063633776546344</v>
       </c>
       <c r="F2" t="n">
-        <v>6.649196042342015</v>
+        <v>1.080494356880578</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.20080806611885</v>
+        <v>8.157631310744312</v>
       </c>
       <c r="D3" t="n">
-        <v>50.0149569791698</v>
+        <v>8.127430509115092</v>
       </c>
       <c r="E3" t="n">
-        <v>6.545438624900579</v>
+        <v>1.063633776546344</v>
       </c>
       <c r="F3" t="n">
-        <v>6.649196042342015</v>
+        <v>1.080494356880578</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.57214365042593</v>
+        <v>10.00547334319421</v>
       </c>
       <c r="D4" t="n">
-        <v>61.37636148674797</v>
+        <v>9.973658741596546</v>
       </c>
       <c r="E4" t="n">
-        <v>6.545438624900579</v>
+        <v>1.063633776546344</v>
       </c>
       <c r="F4" t="n">
-        <v>6.649196042342015</v>
+        <v>1.080494356880578</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.12028292108266</v>
+        <v>8.307045974675932</v>
       </c>
       <c r="D5" t="n">
-        <v>50.79288428008716</v>
+        <v>8.253843695514163</v>
       </c>
       <c r="E5" t="n">
-        <v>6.545438624900579</v>
+        <v>1.063633776546344</v>
       </c>
       <c r="F5" t="n">
-        <v>6.649196042342015</v>
+        <v>1.080494356880578</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.4791731602936</v>
+        <v>7.22786563854771</v>
       </c>
       <c r="D6" t="n">
-        <v>44.20800339121836</v>
+        <v>7.183800551072983</v>
       </c>
       <c r="E6" t="n">
-        <v>6.545438624900579</v>
+        <v>1.063633776546344</v>
       </c>
       <c r="F6" t="n">
-        <v>6.649196042342015</v>
+        <v>1.080494356880578</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>61.46892025863802</v>
+        <v>9.988699542028678</v>
       </c>
       <c r="D7" t="n">
-        <v>61.65199597897173</v>
+        <v>10.01844934658291</v>
       </c>
       <c r="E7" t="n">
-        <v>6.545438624900579</v>
+        <v>1.063633776546344</v>
       </c>
       <c r="F7" t="n">
-        <v>6.649196042342015</v>
+        <v>1.080494356880578</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.40571965593959</v>
+        <v>10.14092944409018</v>
       </c>
       <c r="D8" t="n">
-        <v>62.61059692181567</v>
+        <v>10.17422199979505</v>
       </c>
       <c r="E8" t="n">
-        <v>6.545438624900579</v>
+        <v>1.063633776546344</v>
       </c>
       <c r="F8" t="n">
-        <v>6.649196042342015</v>
+        <v>1.080494356880578</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.71090443095252</v>
+        <v>8.890521970029784</v>
       </c>
       <c r="D9" t="n">
-        <v>54.92938937239832</v>
+        <v>8.926025773014727</v>
       </c>
       <c r="E9" t="n">
-        <v>6.545438624900579</v>
+        <v>1.063633776546344</v>
       </c>
       <c r="F9" t="n">
-        <v>6.649196042342015</v>
+        <v>1.080494356880578</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
